--- a/xls/story.xlsx
+++ b/xls/story.xlsx
@@ -5,13 +5,16 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="qualities" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="討伐令" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="狼患" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="狼皮生意" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="167">
   <si>
     <t>#</t>
   </si>
@@ -49,7 +52,7 @@
     <t>NPC 對玩家的好感度(0~100)，門檻見 GM.FAV；只有 role.json unique:true 的 NPC 存在 quality 庫</t>
   </si>
   <si>
-    <t>QK01_s01</t>
+    <t>討伐令</t>
   </si>
   <si>
     <t>global</t>
@@ -58,40 +61,476 @@
     <t>no</t>
   </si>
   <si>
-    <t>舊任務旗標，階段 2 搬家後刪除</t>
-  </si>
-  <si>
-    <t>QK01_s01_done</t>
-  </si>
-  <si>
-    <t>QK01_map</t>
-  </si>
-  <si>
-    <t>舊任務旗標，階段 2 搬家後刪除(forest-01 的 #QK01_map layer)</t>
-  </si>
-  <si>
-    <t>QX01_s03</t>
-  </si>
-  <si>
-    <t>QX01_s03_done</t>
-  </si>
-  <si>
-    <t>QX01_map</t>
-  </si>
-  <si>
-    <t>舊任務旗標，階段 2 搬家後刪除(forest-01 的 #QX01_map layer)</t>
-  </si>
-  <si>
-    <t>QX02_s01</t>
-  </si>
-  <si>
-    <t>QX02_s01_done</t>
-  </si>
-  <si>
-    <t>quest_done</t>
-  </si>
-  <si>
-    <t>舊任務旗標，階段 2 搬家後刪除(entry 指向不存在的 npc_a_after_quest)</t>
+    <t>黑森林討伐</t>
+  </si>
+  <si>
+    <t>karen 的討伐委託：1 找 xi 了解 / 2 殺狼 / 3 收集匕首 / 4 回報 karen / 10 完成</t>
+  </si>
+  <si>
+    <t>討伐令.殺狼</t>
+  </si>
+  <si>
+    <t>討伐令的殺狼計數器（count 開、stop 停）</t>
+  </si>
+  <si>
+    <t>狼患</t>
+  </si>
+  <si>
+    <t>屠夫的生意經</t>
+  </si>
+  <si>
+    <t>xi 的狼皮委託：1 殺 3 隻狼 / 2 剝狼皮 / 3 狼皮交給 karen / 4 回報 xi / 10 完成</t>
+  </si>
+  <si>
+    <t>狼患.殺狼</t>
+  </si>
+  <si>
+    <t>狼患的殺狼計數器（count 開、stop 停）</t>
+  </si>
+  <si>
+    <t>狼皮生意</t>
+  </si>
+  <si>
+    <t>跑腿的交涉</t>
+  </si>
+  <si>
+    <t>xi 與 karen 的長期收購：1 找 karen 交涉 / 2 回報 xi / 10 完成</t>
+  </si>
+  <si>
+    <t>殺.*</t>
+  </si>
+  <si>
+    <t>全域擊殺累計（殺.&lt;角色id&gt;），角色死亡時自動 +1</t>
+  </si>
+  <si>
+    <t>thread</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>quality</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>journal</t>
+  </si>
+  <si>
+    <t>pos</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>reward_hint</t>
+  </si>
+  <si>
+    <t>黑森林的野狼越來越猖獗，長老需要你的幫助。</t>
+  </si>
+  <si>
+    <t>與 xi 對話了解情況</t>
+  </si>
+  <si>
+    <t>金幣 x100</t>
+  </si>
+  <si>
+    <t>前往黑森林，擊殺黑森林的野狼 ({討伐令.殺狼}/1)</t>
+  </si>
+  <si>
+    <t>m/m_03x05</t>
+  </si>
+  <si>
+    <t>收集匕首</t>
+  </si>
+  <si>
+    <t>任務完成，跟 karen 回報任務</t>
+  </si>
+  <si>
+    <t>已向 karen 回報，領取獎勵</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>who</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>tease</t>
+  </si>
+  <si>
+    <t>requires</t>
+  </si>
+  <si>
+    <t>hint</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>effects</t>
+  </si>
+  <si>
+    <t>hunt_ask</t>
+  </si>
+  <si>
+    <t>karen</t>
+  </si>
+  <si>
+    <t>討伐令==0</t>
+  </si>
+  <si>
+    <t>關於任務</t>
+  </si>
+  <si>
+    <t>@n_hunt_ask</t>
+  </si>
+  <si>
+    <t>hunt_xi</t>
+  </si>
+  <si>
+    <t>xi</t>
+  </si>
+  <si>
+    <t>討伐令==1</t>
+  </si>
+  <si>
+    <t>關於黑森林討伐</t>
+  </si>
+  <si>
+    <t>@n_hunt_xi</t>
+  </si>
+  <si>
+    <t>hunt_kill</t>
+  </si>
+  <si>
+    <t>kill</t>
+  </si>
+  <si>
+    <t>討伐令==2 &amp;&amp; 討伐令.殺狼&gt;=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">討伐令=3 ;
+stop 討伐令.殺狼</t>
+  </si>
+  <si>
+    <t>hunt_knife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item ;
+quality</t>
+  </si>
+  <si>
+    <t>討伐令==3 &amp;&amp; item:sword_01:1</t>
+  </si>
+  <si>
+    <t>討伐令=4</t>
+  </si>
+  <si>
+    <t>hunt_report</t>
+  </si>
+  <si>
+    <t>討伐令&gt;=1 &amp;&amp; 討伐令&lt;10</t>
+  </si>
+  <si>
+    <t>@n_hunt_report</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>node_id</t>
+  </si>
+  <si>
+    <t>label_key</t>
+  </si>
+  <si>
+    <t>text_keys</t>
+  </si>
+  <si>
+    <t>actions</t>
+  </si>
+  <si>
+    <t>next</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>node</t>
+  </si>
+  <si>
+    <t>n_hunt_ask</t>
+  </si>
+  <si>
+    <t>要黑森林討伐?</t>
+  </si>
+  <si>
+    <t>choice</t>
+  </si>
+  <si>
+    <t>接受</t>
+  </si>
+  <si>
+    <t>討伐令=1</t>
+  </si>
+  <si>
+    <t>n_hunt_ask2</t>
+  </si>
+  <si>
+    <t>拒絕</t>
+  </si>
+  <si>
+    <t>n_default</t>
+  </si>
+  <si>
+    <t>先去找xi了解詳情</t>
+  </si>
+  <si>
+    <t>好</t>
+  </si>
+  <si>
+    <t>n_hunt_report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">討伐令&lt;4 : 任務如何了? ;
+討伐令==4 : 任務如何了? ;
+討伐令==10 : 很好，這是你的獎勵</t>
+  </si>
+  <si>
+    <t>處理中</t>
+  </si>
+  <si>
+    <t>討伐令&lt;4</t>
+  </si>
+  <si>
+    <t>完成了</t>
+  </si>
+  <si>
+    <t xml:space="preserve">討伐令=10 ;
+gold+100</t>
+  </si>
+  <si>
+    <t>討伐令==4</t>
+  </si>
+  <si>
+    <t>離開</t>
+  </si>
+  <si>
+    <t>討伐令==10</t>
+  </si>
+  <si>
+    <t>n_hunt_xi</t>
+  </si>
+  <si>
+    <t>前往黑森林，擊殺黑森林的野狼</t>
+  </si>
+  <si>
+    <t>了解</t>
+  </si>
+  <si>
+    <t xml:space="preserve">討伐令=2 ;
+count 討伐令.殺狼 kill:wolf</t>
+  </si>
+  <si>
+    <t>黑森林的野狼氾濫，xi 的肉舖快沒貨了，想找人幫忙獵狼取皮，順便帶個口信給城裡的商人 karen。</t>
+  </si>
+  <si>
+    <t>前往黑森林狩獵，擊殺野狼 ({狼患.殺狼}/3)</t>
+  </si>
+  <si>
+    <t>金幣 x120、斧頭 x1</t>
+  </si>
+  <si>
+    <t>剝下狼皮</t>
+  </si>
+  <si>
+    <t>帶著狼皮去找商人 karen 談談</t>
+  </si>
+  <si>
+    <t>任務完成，回去跟 xi 回報</t>
+  </si>
+  <si>
+    <t>已向 xi 回報，領取獎勵</t>
+  </si>
+  <si>
+    <t>wolf_ask</t>
+  </si>
+  <si>
+    <t>狼患==0</t>
+  </si>
+  <si>
+    <t>@n_wolf_ask</t>
+  </si>
+  <si>
+    <t>wolf_kill</t>
+  </si>
+  <si>
+    <t>狼患==1 &amp;&amp; 狼患.殺狼&gt;=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狼患=2 ;
+stop 狼患.殺狼</t>
+  </si>
+  <si>
+    <t>wolf_pelt</t>
+  </si>
+  <si>
+    <t>狼患==2 &amp;&amp; item:plet:1</t>
+  </si>
+  <si>
+    <t>狼患=3</t>
+  </si>
+  <si>
+    <t>wolf_karen</t>
+  </si>
+  <si>
+    <t>狼患==3 &amp;&amp; item:plet:1</t>
+  </si>
+  <si>
+    <t>關於黑森林的狼皮</t>
+  </si>
+  <si>
+    <t>@n_wolf_karen</t>
+  </si>
+  <si>
+    <t>wolf_report</t>
+  </si>
+  <si>
+    <t>狼患&gt;=1 &amp;&amp; 狼患&lt;10</t>
+  </si>
+  <si>
+    <t>@n_wolf_report</t>
+  </si>
+  <si>
+    <t>n_wolf_ask</t>
+  </si>
+  <si>
+    <t>最近黑森林的狼變多了，肉舖都要沒貨了……能幫我獵些狼皮回來嗎？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狼患=1 ;
+count 狼患.殺狼 kill:wolf</t>
+  </si>
+  <si>
+    <t>n_wolf_report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狼患&lt;4 : 狼皮收集得如何了? ;
+狼患==4 : 都準備好了嗎？太好了! ;
+狼患==10 : 謝謝你，這是你的獎勵</t>
+  </si>
+  <si>
+    <t>狼患&lt;4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狼患=10 ;
+gold+120 ;
+give axe_01 1</t>
+  </si>
+  <si>
+    <t>狼患==4</t>
+  </si>
+  <si>
+    <t>狼患==10</t>
+  </si>
+  <si>
+    <t>n_wolf_karen</t>
+  </si>
+  <si>
+    <t>這批狼皮品質不錯，這批貨我收了！幫我跟 xi 說一聲喔。</t>
+  </si>
+  <si>
+    <t>好的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">take plet 1 ;
+狼患=4</t>
+  </si>
+  <si>
+    <t>黑森林的野狼問題解決後，xi 想跟 karen 談長期收購狼皮的生意，請你幫忙帶提案去交涉。</t>
+  </si>
+  <si>
+    <t>帶著提案去找商人 karen 談交涉條件</t>
+  </si>
+  <si>
+    <t>已向 xi 回報，領取謝禮</t>
+  </si>
+  <si>
+    <t>trade_ask</t>
+  </si>
+  <si>
+    <t>狼患==10 &amp;&amp; 狼皮生意==0</t>
+  </si>
+  <si>
+    <t>@n_trade_ask</t>
+  </si>
+  <si>
+    <t>trade_karen</t>
+  </si>
+  <si>
+    <t>狼皮生意==1</t>
+  </si>
+  <si>
+    <t>轉達 xi 的提案</t>
+  </si>
+  <si>
+    <t>@n_trade_karen</t>
+  </si>
+  <si>
+    <t>trade_report</t>
+  </si>
+  <si>
+    <t>狼皮生意&gt;=1 &amp;&amp; 狼皮生意&lt;10</t>
+  </si>
+  <si>
+    <t>@n_trade_report</t>
+  </si>
+  <si>
+    <t>n_trade_ask</t>
+  </si>
+  <si>
+    <t>森林安靜多了，這下該跟 karen 把長期收購狼皮的事情談攏。你能不能幫我帶個提案去，跟她把價錢跟數量談好？</t>
+  </si>
+  <si>
+    <t>狼皮生意=1</t>
+  </si>
+  <si>
+    <t>n_trade_report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狼皮生意==1 : 跟 karen 談得怎麼樣了? ;
+狼皮生意==2 : 都談好了嗎？太好了! ;
+狼皮生意==10 : 這趟辛苦你了，這是謝禮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狼皮生意=10 ;
+gold+100</t>
+  </si>
+  <si>
+    <t>狼皮生意==2</t>
+  </si>
+  <si>
+    <t>狼皮生意==10</t>
+  </si>
+  <si>
+    <t>n_trade_karen</t>
+  </si>
+  <si>
+    <t>長期收購？聽起來不錯，價錢我可以再加一點，你回去跟 xi 說一聲，這筆生意我接了。</t>
+  </si>
+  <si>
+    <t>狼皮生意=2</t>
   </si>
 </sst>
 </file>
@@ -118,7 +557,7 @@
       <name val="微軟正黑體 Light"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,6 +572,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.7999816888943144"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.7999816888943144"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.3999755851924192"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.7999816888943144"/>
       </patternFill>
     </fill>
   </fills>
@@ -162,6 +616,20 @@
       <left/>
       <right style="thin"/>
       <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -172,25 +640,11 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -206,10 +660,40 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -551,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -605,7 +1089,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
       <c r="B3" s="5" t="s">
         <v>12</v>
@@ -619,15 +1103,17 @@
       <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="G3" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>13</v>
@@ -640,13 +1126,13 @@
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -657,15 +1143,17 @@
       <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="G5" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>13</v>
@@ -678,13 +1166,13 @@
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>13</v>
@@ -695,15 +1183,17 @@
       <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="G7" s="6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>13</v>
@@ -716,68 +1206,1417 @@
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8">
+        <v>2</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8">
+        <v>3</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8">
+        <v>4</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10">
+        <v>10</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="21" ht="94.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="J22" s="16"/>
+    </row>
+    <row r="23" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="J23" s="16"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="J24" s="16"/>
+    </row>
+    <row r="25" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+    </row>
+    <row r="26" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" ht="126" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8">
+        <v>2</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8">
+        <v>3</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8">
+        <v>4</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10">
+        <v>10</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" ht="94.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="21" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="J21" s="16"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="J22" s="16"/>
+    </row>
+    <row r="23" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+    </row>
+    <row r="24" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" ht="110.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8">
+        <v>2</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10">
+        <v>10</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="J7" s="12"/>
+    </row>
+    <row r="8" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" ht="78.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" ht="94.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/xls/story.xlsx
+++ b/xls/story.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="174">
   <si>
     <t>#</t>
   </si>
@@ -343,6 +343,18 @@
 count 討伐令.殺狼 kill:wolf</t>
   </si>
   <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>盜賊</t>
+  </si>
+  <si>
+    <t>討伐令 &amp;&amp; 討伐令&lt;10</t>
+  </si>
+  <si>
+    <t>討伐令進行中，m_03x05 出現 3 個 rogue</t>
+  </si>
+  <si>
     <t>黑森林的野狼氾濫，xi 的肉舖快沒貨了，想找人幫忙獵狼取皮，順便帶個口信給城裡的商人 karen。</t>
   </si>
   <si>
@@ -456,6 +468,15 @@
   <si>
     <t xml:space="preserve">take plet 1 ;
 狼患=4</t>
+  </si>
+  <si>
+    <t>狼群</t>
+  </si>
+  <si>
+    <t>狼患 &amp;&amp; 狼患&lt;10</t>
+  </si>
+  <si>
+    <t>狼患進行中，m_03x05 出現 3 隻狼</t>
   </si>
   <si>
     <t>黑森林的野狼問題解決後，xi 想跟 karen 談長期收購狼皮的生意，請你幫忙帶提案去交涉。</t>
@@ -1217,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1725,6 +1746,31 @@
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
     </row>
+    <row r="28" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" ht="31.5" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
@@ -1733,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1788,7 +1834,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>19</v>
@@ -1797,14 +1843,14 @@
         <v>1</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>41</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="8" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
@@ -1816,7 +1862,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
@@ -1831,7 +1877,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
@@ -1846,7 +1892,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
@@ -1861,7 +1907,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H6" s="10"/>
       <c r="I6" s="10" t="s">
@@ -1903,7 +1949,7 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>60</v>
@@ -1911,20 +1957,20 @@
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>57</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J9" s="12"/>
     </row>
     <row r="10" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
@@ -1932,18 +1978,18 @@
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
@@ -1951,18 +1997,18 @@
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>55</v>
@@ -1970,20 +2016,20 @@
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J12" s="12"/>
     </row>
     <row r="13" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>60</v>
@@ -1991,14 +2037,14 @@
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>57</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="J13" s="14"/>
     </row>
@@ -2042,11 +2088,11 @@
         <v>60</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="16" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
@@ -2064,7 +2110,7 @@
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="16" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H17" s="16" t="s">
         <v>91</v>
@@ -2097,11 +2143,11 @@
         <v>60</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
@@ -2123,7 +2169,7 @@
         <v>91</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J20" s="16"/>
     </row>
@@ -2138,13 +2184,13 @@
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J21" s="16"/>
     </row>
@@ -2163,7 +2209,7 @@
         <v>91</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J22" s="16"/>
     </row>
@@ -2175,11 +2221,11 @@
         <v>55</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E23" s="16"/>
       <c r="F23" s="16" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
@@ -2193,17 +2239,42 @@
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
       <c r="E24" s="18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F24" s="18"/>
       <c r="G24" s="18" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H24" s="18" t="s">
         <v>91</v>
       </c>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" ht="31.5" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>149</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2268,7 +2339,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>24</v>
@@ -2277,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -2294,7 +2365,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
@@ -2309,7 +2380,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10" t="s">
@@ -2351,7 +2422,7 @@
     </row>
     <row r="7" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>60</v>
@@ -2359,20 +2430,20 @@
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>57</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="J7" s="12"/>
     </row>
     <row r="8" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>55</v>
@@ -2380,20 +2451,20 @@
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="J8" s="12"/>
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>60</v>
@@ -2401,14 +2472,14 @@
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>57</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="J9" s="14"/>
     </row>
@@ -2452,11 +2523,11 @@
         <v>60</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="16" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
@@ -2474,7 +2545,7 @@
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="16" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H13" s="16" t="s">
         <v>91</v>
@@ -2507,11 +2578,11 @@
         <v>60</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="16" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
@@ -2533,7 +2604,7 @@
         <v>91</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="J16" s="16"/>
     </row>
@@ -2548,13 +2619,13 @@
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="16" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="J17" s="16"/>
     </row>
@@ -2573,7 +2644,7 @@
         <v>91</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="J18" s="16"/>
     </row>
@@ -2585,11 +2656,11 @@
         <v>55</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
@@ -2603,11 +2674,11 @@
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
       <c r="E20" s="18" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="18" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H20" s="18" t="s">
         <v>91</v>

--- a/xls/story.xlsx
+++ b/xls/story.xlsx
@@ -61,16 +61,16 @@
     <t>no</t>
   </si>
   <si>
-    <t>黑森林討伐</t>
-  </si>
-  <si>
-    <t>karen 的討伐委託：1 找 xi 了解 / 2 殺狼 / 3 收集匕首 / 4 回報 karen / 10 完成</t>
-  </si>
-  <si>
-    <t>討伐令.殺狼</t>
-  </si>
-  <si>
-    <t>討伐令的殺狼計數器（count 開、stop 停）</t>
+    <t>盜賊討伐</t>
+  </si>
+  <si>
+    <t>karen 的討伐委託：1 找 xi 了解 / 2 殺盜賊 / 3 收集匕首 / 4 回報 karen / 10 完成</t>
+  </si>
+  <si>
+    <t>討伐令.殺盜賊</t>
+  </si>
+  <si>
+    <t>討伐令的殺盜賊計數器（count 開、stop 停）</t>
   </si>
   <si>
     <t>狼患</t>
@@ -127,7 +127,7 @@
     <t>reward_hint</t>
   </si>
   <si>
-    <t>黑森林的野狼越來越猖獗，長老需要你的幫助。</t>
+    <t>黑森林裡出現了一群盜賊，商隊都不敢上路，商人 karen 需要你的幫助。</t>
   </si>
   <si>
     <t>與 xi 對話了解情況</t>
@@ -136,13 +136,13 @@
     <t>金幣 x100</t>
   </si>
   <si>
-    <t>前往黑森林，擊殺黑森林的野狼 ({討伐令.殺狼}/1)</t>
+    <t>前往黑森林，擊殺盜賊 ({討伐令.殺盜賊}/1)</t>
   </si>
   <si>
     <t>m/m_03x05</t>
   </si>
   <si>
-    <t>收集匕首</t>
+    <t>從盜賊身上取得匕首</t>
   </si>
   <si>
     <t>任務完成，跟 karen 回報任務</t>
@@ -202,7 +202,7 @@
     <t>討伐令==1</t>
   </si>
   <si>
-    <t>關於黑森林討伐</t>
+    <t>關於盜賊</t>
   </si>
   <si>
     <t>@n_hunt_xi</t>
@@ -214,11 +214,11 @@
     <t>kill</t>
   </si>
   <si>
-    <t>討伐令==2 &amp;&amp; 討伐令.殺狼&gt;=1</t>
+    <t>討伐令==2 &amp;&amp; 討伐令.殺盜賊&gt;=1</t>
   </si>
   <si>
     <t xml:space="preserve">討伐令=3 ;
-stop 討伐令.殺狼</t>
+stop 討伐令.殺盜賊</t>
   </si>
   <si>
     <t>hunt_knife</t>
@@ -273,7 +273,7 @@
     <t>n_hunt_ask</t>
   </si>
   <si>
-    <t>要黑森林討伐?</t>
+    <t>最近黑森林有盜賊出沒，商隊都不敢走了……能幫忙討伐嗎?</t>
   </si>
   <si>
     <t>choice</t>
@@ -333,14 +333,14 @@
     <t>n_hunt_xi</t>
   </si>
   <si>
-    <t>前往黑森林，擊殺黑森林的野狼</t>
+    <t>盜賊就躲在黑森林裡，他們身上都帶著匕首，拿一把回來給 karen 當證明吧。</t>
   </si>
   <si>
     <t>了解</t>
   </si>
   <si>
     <t xml:space="preserve">討伐令=2 ;
-count 討伐令.殺狼 kill:wolf</t>
+count 討伐令.殺盜賊 kill:rogue-1</t>
   </si>
   <si>
     <t>group</t>

--- a/xls/story.xlsx
+++ b/xls/story.xlsx
@@ -136,7 +136,7 @@
     <t>金幣 x100</t>
   </si>
   <si>
-    <t>前往黑森林，擊殺盜賊 ({討伐令.殺盜賊}/1)</t>
+    <t>前往黑森林，清光盜賊 ({討伐令.殺盜賊}/3)</t>
   </si>
   <si>
     <t>m/m_03x05</t>
@@ -214,7 +214,7 @@
     <t>kill</t>
   </si>
   <si>
-    <t>討伐令==2 &amp;&amp; 討伐令.殺盜賊&gt;=1</t>
+    <t>討伐令==2 &amp;&amp; 討伐令.殺盜賊&gt;=3</t>
   </si>
   <si>
     <t xml:space="preserve">討伐令=3 ;

--- a/xls/story.xlsx
+++ b/xls/story.xlsx
@@ -349,10 +349,10 @@
     <t>盜賊</t>
   </si>
   <si>
-    <t>討伐令 &amp;&amp; 討伐令&lt;10</t>
-  </si>
-  <si>
-    <t>討伐令進行中，m_03x05 出現 3 個 rogue</t>
+    <t>討伐令&gt;=2 &amp;&amp; 討伐令&lt;10</t>
+  </si>
+  <si>
+    <t>跟 xi 談過之後（討伐令&gt;=2）m_03x05 才出現 3 個 rogue，跟擊殺計數同時開始</t>
   </si>
   <si>
     <t>黑森林的野狼氾濫，xi 的肉舖快沒貨了，想找人幫忙獵狼取皮，順便帶個口信給城裡的商人 karen。</t>

--- a/xls/story.xlsx
+++ b/xls/story.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="175">
   <si>
     <t>#</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>effects</t>
+  </si>
+  <si>
+    <t>mood</t>
   </si>
   <si>
     <t>hunt_ask</t>
@@ -1238,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1251,6 +1254,7 @@
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="34" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1285,7 +1289,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
@@ -1310,7 +1314,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1327,7 +1331,7 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1342,7 +1346,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1357,7 +1361,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1374,7 +1378,8 @@
       </c>
       <c r="J6" s="10"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1405,353 +1410,363 @@
       <c r="J8" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J9" s="12"/>
-    </row>
-    <row r="10" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J10" s="12"/>
-    </row>
-    <row r="11" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" ht="47.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J13" s="14"/>
-    </row>
+      <c r="K13" s="14"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="15" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I17" s="16"/>
       <c r="J17" s="16"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
       <c r="H18" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="16"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I20" s="16"/>
       <c r="J20" s="16"/>
     </row>
-    <row r="21" ht="94.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" ht="94.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="I21" s="16"/>
       <c r="J21" s="16"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J22" s="16"/>
     </row>
-    <row r="23" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
       <c r="E23" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J23" s="16"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
       <c r="E24" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="16"/>
       <c r="H24" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J24" s="16"/>
     </row>
-    <row r="25" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E25" s="16"/>
       <c r="F25" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
     </row>
-    <row r="26" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B26" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
       <c r="E26" s="18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="18"/>
       <c r="G26" s="18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
     </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="28" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>50</v>
@@ -1760,15 +1775,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" ht="31.5" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1779,7 +1794,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1792,6 +1807,7 @@
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="34" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1826,7 +1842,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" ht="126" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="126" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>19</v>
       </c>
@@ -1834,7 +1850,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>19</v>
@@ -1843,17 +1859,17 @@
         <v>1</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>41</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1862,13 +1878,13 @@
         <v>2</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1877,13 +1893,13 @@
         <v>3</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1892,13 +1908,13 @@
         <v>4</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1907,7 +1923,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H6" s="10"/>
       <c r="I6" s="10" t="s">
@@ -1915,7 +1931,8 @@
       </c>
       <c r="J6" s="10"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -1946,317 +1963,327 @@
       <c r="J8" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J9" s="12"/>
-    </row>
-    <row r="10" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J12" s="12"/>
-    </row>
-    <row r="13" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
       <c r="F13" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J13" s="14"/>
-    </row>
+      <c r="K13" s="14"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="15" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I17" s="16"/>
       <c r="J17" s="16"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
       <c r="H18" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I18" s="16"/>
       <c r="J18" s="16"/>
     </row>
-    <row r="19" ht="94.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" ht="94.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J20" s="16"/>
     </row>
-    <row r="21" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J21" s="16"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J22" s="16"/>
     </row>
-    <row r="23" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E23" s="16"/>
       <c r="F23" s="16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
       <c r="I23" s="16"/>
       <c r="J23" s="16"/>
     </row>
-    <row r="24" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B24" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
       <c r="E24" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F24" s="18"/>
       <c r="G24" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
     </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="26" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>50</v>
@@ -2265,15 +2292,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" ht="31.5" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2284,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2297,6 +2324,7 @@
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="34" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2331,7 +2359,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" ht="110.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="110.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>24</v>
       </c>
@@ -2339,7 +2367,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>24</v>
@@ -2348,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -2356,7 +2384,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -2365,13 +2393,13 @@
         <v>2</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -2380,7 +2408,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10" t="s">
@@ -2388,7 +2416,8 @@
       </c>
       <c r="J4" s="10"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="6" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -2419,269 +2448,276 @@
       <c r="J6" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J7" s="12"/>
-    </row>
-    <row r="8" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="12"/>
+    </row>
+    <row r="8" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J8" s="12"/>
-    </row>
-    <row r="9" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J9" s="14"/>
-    </row>
+      <c r="K9" s="14"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="11" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" ht="78.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
       <c r="H14" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
     </row>
-    <row r="15" ht="94.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" ht="94.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
       <c r="E16" s="16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="16"/>
       <c r="H16" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J17" s="16"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
       <c r="H18" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J18" s="16"/>
     </row>
-    <row r="19" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
       <c r="E20" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>

--- a/xls/story.xlsx
+++ b/xls/story.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="193">
   <si>
     <t>#</t>
   </si>
@@ -376,6 +376,9 @@
     <t>任務完成，回去跟 xi 回報</t>
   </si>
   <si>
+    <t>你把狼皮直接賣給了 xi</t>
+  </si>
+  <si>
     <t>已向 xi 回報，領取獎勵</t>
   </si>
   <si>
@@ -422,10 +425,45 @@
     <t>wolf_report</t>
   </si>
   <si>
-    <t>狼患&gt;=1 &amp;&amp; 狼患&lt;10</t>
+    <t>狼患&gt;=1 &amp;&amp; 狼患&lt;9</t>
   </si>
   <si>
     <t>@n_wolf_report</t>
+  </si>
+  <si>
+    <t>wolf_sell</t>
+  </si>
+  <si>
+    <t>狼患==2</t>
+  </si>
+  <si>
+    <t>把狼皮直接賣給你</t>
+  </si>
+  <si>
+    <t>需要狼皮</t>
+  </si>
+  <si>
+    <t>……也好，省得你跑一趟，那我自己收了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">take plet 1 ;
+狼患=9 ;
+gold+80</t>
+  </si>
+  <si>
+    <t>wolf_grudge</t>
+  </si>
+  <si>
+    <t>see</t>
+  </si>
+  <si>
+    <t>狼患==9 &amp;&amp; !_grudge</t>
+  </si>
+  <si>
+    <t>喂！你給我過來！</t>
+  </si>
+  <si>
+    <t>approach n_wolf_grudge</t>
   </si>
   <si>
     <t>n_wolf_ask</t>
@@ -473,10 +511,30 @@
 狼患=4</t>
   </si>
   <si>
+    <t>n_wolf_grudge</t>
+  </si>
+  <si>
+    <t>聽說你把狼皮都賣給 xi 了？哼，有好貨不先找我，倒便宜了那個屠夫。</t>
+  </si>
+  <si>
+    <t>抱歉，下次一定先找你</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_grudge=1 ;
+好感-5</t>
+  </si>
+  <si>
+    <t>我想賣給誰就賣給誰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_grudge=1 ;
+好感-15</t>
+  </si>
+  <si>
     <t>狼群</t>
   </si>
   <si>
-    <t>狼患 &amp;&amp; 狼患&lt;10</t>
+    <t>狼患 &amp;&amp; 狼患&lt;9</t>
   </si>
   <si>
     <t>狼患進行中，m_03x05 出現 3 隻狼</t>
@@ -702,22 +760,22 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1289,7 +1347,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
@@ -1314,7 +1372,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1331,7 +1389,7 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1346,7 +1404,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1361,7 +1419,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -1378,7 +1436,6 @@
       </c>
       <c r="J6" s="10"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
@@ -1414,7 +1471,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>55</v>
       </c>
@@ -1436,7 +1493,7 @@
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>60</v>
       </c>
@@ -1458,7 +1515,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" ht="47.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" ht="47.25" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>65</v>
       </c>
@@ -1478,7 +1535,7 @@
       </c>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>69</v>
       </c>
@@ -1498,29 +1555,28 @@
       </c>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="13" t="s">
+    <row r="13" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14" t="s">
+      <c r="H13" s="12"/>
+      <c r="I13" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+    </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>0</v>
@@ -1553,214 +1609,213 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="15" t="s">
+    <row r="16" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16" t="s">
+      <c r="E16" s="14"/>
+      <c r="F16" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="15" t="s">
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16" t="s">
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16" t="s">
+      <c r="F17" s="14"/>
+      <c r="G17" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="15" t="s">
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16" t="s">
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16" t="s">
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="15" t="s">
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16" t="s">
+      <c r="E19" s="14"/>
+      <c r="F19" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16" t="s">
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16" t="s">
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-    </row>
-    <row r="21" ht="94.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="15" t="s">
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" ht="94.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16" t="s">
+      <c r="E21" s="14"/>
+      <c r="F21" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="15" t="s">
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16" t="s">
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16" t="s">
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="16" t="s">
+      <c r="I22" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="J22" s="16"/>
-    </row>
-    <row r="23" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="15" t="s">
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16" t="s">
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16" t="s">
+      <c r="F23" s="14"/>
+      <c r="G23" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="J23" s="16"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="15" t="s">
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16" t="s">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16" t="s">
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I24" s="16" t="s">
+      <c r="I24" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="J24" s="16"/>
-    </row>
-    <row r="25" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="15" t="s">
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16" t="s">
+      <c r="E25" s="14"/>
+      <c r="F25" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="17" t="s">
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18" t="s">
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18" t="s">
+      <c r="F26" s="14"/>
+      <c r="G26" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="H26" s="18" t="s">
+      <c r="H26" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>0</v>
@@ -1775,7 +1830,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" ht="31.5" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>109</v>
       </c>
@@ -1794,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1810,7 +1865,7 @@
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1899,7 +1954,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1915,392 +1970,518 @@
       <c r="J5" s="8"/>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10">
+      <c r="B6" s="7"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="8">
+        <v>9</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10">
         <v>10</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10" t="s">
+      <c r="G7" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="12" t="s">
+    <row r="10" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-    </row>
-    <row r="10" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12" t="s">
-        <v>66</v>
-      </c>
+      <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="G10" s="12"/>
+        <v>121</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>58</v>
+      </c>
       <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12" t="s">
-        <v>124</v>
-      </c>
+      <c r="I10" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
     <row r="11" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K11" s="12"/>
     </row>
     <row r="12" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="12"/>
+        <v>126</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="E12" s="12"/>
       <c r="F12" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="C13" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12" t="s">
+      <c r="G13" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-    </row>
-    <row r="13" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="13" t="s">
+      <c r="H13" s="12"/>
+      <c r="I13" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="G13" s="14" t="s">
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="H14" s="12"/>
+      <c r="I14" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" ht="47.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="K15" s="14"/>
+    </row>
+    <row r="16" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" s="17"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="15" t="s">
+    <row r="19" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C19" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="15" t="s">
+      <c r="D19" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16" t="s">
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="H17" s="16" t="s">
+      <c r="F20" s="14"/>
+      <c r="G20" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="15" t="s">
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16" t="s">
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16" t="s">
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-    </row>
-    <row r="19" ht="94.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="15" t="s">
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" ht="94.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C22" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
+      <c r="D22" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16" t="s">
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16" t="s">
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I20" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="J20" s="16"/>
-    </row>
-    <row r="21" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="15" t="s">
+      <c r="I23" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16" t="s">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="J21" s="16"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="15" t="s">
+      <c r="F24" s="14"/>
+      <c r="G24" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16" t="s">
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16" t="s">
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="J22" s="16"/>
-    </row>
-    <row r="23" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="15" t="s">
+      <c r="I25" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C26" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-    </row>
-    <row r="24" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="17" t="s">
+      <c r="D26" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" ht="47.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="H24" s="18" t="s">
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="H27" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>150</v>
+    <row r="33" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2359,7 +2540,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" ht="110.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="110.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>24</v>
       </c>
@@ -2367,7 +2548,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>24</v>
@@ -2376,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -2384,7 +2565,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -2399,7 +2580,7 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -2408,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10" t="s">
@@ -2416,7 +2597,6 @@
       </c>
       <c r="J4" s="10"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25"/>
     <row r="6" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
@@ -2452,9 +2632,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>61</v>
@@ -2462,21 +2642,21 @@
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>58</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
     </row>
-    <row r="8" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>56</v>
@@ -2484,41 +2664,40 @@
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" s="14" t="s">
+    <row r="9" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="G9" s="14" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+    </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>0</v>
@@ -2551,176 +2730,176 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="15" t="s">
+    <row r="12" ht="78.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="15" t="s">
+      <c r="D12" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16" t="s">
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="16" t="s">
+      <c r="F13" s="14"/>
+      <c r="G13" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="15" t="s">
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16" t="s">
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16" t="s">
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-    </row>
-    <row r="15" ht="94.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="15" t="s">
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" ht="94.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="15" t="s">
+      <c r="D15" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16" t="s">
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16" t="s">
+      <c r="F20" s="14"/>
+      <c r="G20" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="H20" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="J18" s="16"/>
-    </row>
-    <row r="19" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/xls/story.xlsx
+++ b/xls/story.xlsx
@@ -37,7 +37,7 @@
     <t>desc</t>
   </si>
   <si>
-    <t>好感</t>
+    <t>favor</t>
   </si>
   <si>
     <t>npc</t>
@@ -52,7 +52,7 @@
     <t>NPC 對玩家的好感度(0~100)，門檻見 GM.FAV；只有 role.json unique:true 的 NPC 存在 quality 庫</t>
   </si>
   <si>
-    <t>討伐令</t>
+    <t>bandit_hunt</t>
   </si>
   <si>
     <t>global</t>
@@ -67,13 +67,13 @@
     <t>karen 的討伐委託：1 找 xi 了解 / 2 殺盜賊 / 3 收集匕首 / 4 回報 karen / 10 完成</t>
   </si>
   <si>
-    <t>討伐令.殺盜賊</t>
+    <t>bandit_hunt.kills</t>
   </si>
   <si>
     <t>討伐令的殺盜賊計數器（count 開、stop 停）</t>
   </si>
   <si>
-    <t>狼患</t>
+    <t>wolf</t>
   </si>
   <si>
     <t>屠夫的生意經</t>
@@ -82,13 +82,13 @@
     <t>xi 的狼皮委託：1 殺 3 隻狼 / 2 剝狼皮 / 3 狼皮交給 karen / 4 回報 xi / 10 完成</t>
   </si>
   <si>
-    <t>狼患.殺狼</t>
+    <t>wolf.kills</t>
   </si>
   <si>
     <t>狼患的殺狼計數器（count 開、stop 停）</t>
   </si>
   <si>
-    <t>狼皮生意</t>
+    <t>pelt_trade</t>
   </si>
   <si>
     <t>跑腿的交涉</t>
@@ -97,7 +97,7 @@
     <t>xi 與 karen 的長期收購：1 找 karen 交涉 / 2 回報 xi / 10 完成</t>
   </si>
   <si>
-    <t>殺.*</t>
+    <t>kill.*</t>
   </si>
   <si>
     <t>全域擊殺累計（殺.&lt;角色id&gt;），角色死亡時自動 +1</t>
@@ -136,7 +136,7 @@
     <t>金幣 x100</t>
   </si>
   <si>
-    <t>前往黑森林，清光盜賊 ({討伐令.殺盜賊}/3)</t>
+    <t>前往黑森林，清光盜賊 ({bandit_hunt.kills}/3)</t>
   </si>
   <si>
     <t>m/m_03x05</t>
@@ -187,7 +187,7 @@
     <t>karen</t>
   </si>
   <si>
-    <t>討伐令==0</t>
+    <t>bandit_hunt==0</t>
   </si>
   <si>
     <t>關於任務</t>
@@ -202,7 +202,7 @@
     <t>xi</t>
   </si>
   <si>
-    <t>討伐令==1</t>
+    <t>bandit_hunt==1</t>
   </si>
   <si>
     <t>關於盜賊</t>
@@ -217,11 +217,11 @@
     <t>kill</t>
   </si>
   <si>
-    <t>討伐令==2 &amp;&amp; 討伐令.殺盜賊&gt;=3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">討伐令=3 ;
-stop 討伐令.殺盜賊</t>
+    <t>bandit_hunt==2 &amp;&amp; bandit_hunt.kills&gt;=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bandit_hunt=3 ;
+stop bandit_hunt.kills</t>
   </si>
   <si>
     <t>hunt_knife</t>
@@ -231,16 +231,16 @@
 quality</t>
   </si>
   <si>
-    <t>討伐令==3 &amp;&amp; item:sword_01:1</t>
-  </si>
-  <si>
-    <t>討伐令=4</t>
+    <t>bandit_hunt==3 &amp;&amp; item:sword_01:1</t>
+  </si>
+  <si>
+    <t>bandit_hunt=4</t>
   </si>
   <si>
     <t>hunt_report</t>
   </si>
   <si>
-    <t>討伐令&gt;=1 &amp;&amp; 討伐令&lt;10</t>
+    <t>bandit_hunt&gt;=1 &amp;&amp; bandit_hunt&lt;10</t>
   </si>
   <si>
     <t>@n_hunt_report</t>
@@ -285,7 +285,7 @@
     <t>接受</t>
   </si>
   <si>
-    <t>討伐令=1</t>
+    <t>bandit_hunt=1</t>
   </si>
   <si>
     <t>n_hunt_ask2</t>
@@ -306,31 +306,31 @@
     <t>n_hunt_report</t>
   </si>
   <si>
-    <t xml:space="preserve">討伐令&lt;4 : 任務如何了? ;
-討伐令==4 : 任務如何了? ;
-討伐令==10 : 很好，這是你的獎勵</t>
+    <t xml:space="preserve">bandit_hunt&lt;4 : 任務如何了? ;
+bandit_hunt==4 : 任務如何了? ;
+bandit_hunt==10 : 很好，這是你的獎勵</t>
   </si>
   <si>
     <t>處理中</t>
   </si>
   <si>
-    <t>討伐令&lt;4</t>
+    <t>bandit_hunt&lt;4</t>
   </si>
   <si>
     <t>完成了</t>
   </si>
   <si>
-    <t xml:space="preserve">討伐令=10 ;
+    <t xml:space="preserve">bandit_hunt=10 ;
 gold+100</t>
   </si>
   <si>
-    <t>討伐令==4</t>
+    <t>bandit_hunt==4</t>
   </si>
   <si>
     <t>離開</t>
   </si>
   <si>
-    <t>討伐令==10</t>
+    <t>bandit_hunt==10</t>
   </si>
   <si>
     <t>n_hunt_xi</t>
@@ -342,17 +342,17 @@
     <t>了解</t>
   </si>
   <si>
-    <t xml:space="preserve">討伐令=2 ;
-count 討伐令.殺盜賊 kill:rogue-1</t>
+    <t xml:space="preserve">bandit_hunt=2 ;
+count bandit_hunt.kills kill:rogue-1</t>
   </si>
   <si>
     <t>group</t>
   </si>
   <si>
-    <t>盜賊</t>
-  </si>
-  <si>
-    <t>討伐令&gt;=2 &amp;&amp; 討伐令&lt;10</t>
+    <t>bandits</t>
+  </si>
+  <si>
+    <t>bandit_hunt&gt;=2 &amp;&amp; bandit_hunt&lt;10</t>
   </si>
   <si>
     <t>跟 xi 談過之後（討伐令&gt;=2）m_03x05 才出現 3 個 rogue，跟擊殺計數同時開始</t>
@@ -361,7 +361,7 @@
     <t>黑森林的野狼氾濫，xi 的肉舖快沒貨了，想找人幫忙獵狼取皮，順便帶個口信給城裡的商人 karen。</t>
   </si>
   <si>
-    <t>前往黑森林狩獵，擊殺野狼 ({狼患.殺狼}/3)</t>
+    <t>前往黑森林狩獵，擊殺野狼 ({wolf.kills}/3)</t>
   </si>
   <si>
     <t>金幣 x120、斧頭 x1</t>
@@ -385,7 +385,7 @@
     <t>wolf_ask</t>
   </si>
   <si>
-    <t>狼患==0</t>
+    <t>wolf==0</t>
   </si>
   <si>
     <t>@n_wolf_ask</t>
@@ -394,26 +394,26 @@
     <t>wolf_kill</t>
   </si>
   <si>
-    <t>狼患==1 &amp;&amp; 狼患.殺狼&gt;=3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">狼患=2 ;
-stop 狼患.殺狼</t>
+    <t>wolf==1 &amp;&amp; wolf.kills&gt;=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wolf=2 ;
+stop wolf.kills</t>
   </si>
   <si>
     <t>wolf_pelt</t>
   </si>
   <si>
-    <t>狼患==2 &amp;&amp; item:plet:1</t>
-  </si>
-  <si>
-    <t>狼患=3</t>
+    <t>wolf==2 &amp;&amp; item:plet:1</t>
+  </si>
+  <si>
+    <t>wolf=3</t>
   </si>
   <si>
     <t>wolf_karen</t>
   </si>
   <si>
-    <t>狼患==3 &amp;&amp; item:plet:1</t>
+    <t>wolf==3 &amp;&amp; item:plet:1</t>
   </si>
   <si>
     <t>關於黑森林的狼皮</t>
@@ -425,7 +425,7 @@
     <t>wolf_report</t>
   </si>
   <si>
-    <t>狼患&gt;=1 &amp;&amp; 狼患&lt;9</t>
+    <t>wolf&gt;=1 &amp;&amp; wolf&lt;9</t>
   </si>
   <si>
     <t>@n_wolf_report</t>
@@ -434,7 +434,7 @@
     <t>wolf_sell</t>
   </si>
   <si>
-    <t>狼患==2</t>
+    <t>wolf==2</t>
   </si>
   <si>
     <t>把狼皮直接賣給你</t>
@@ -447,7 +447,7 @@
   </si>
   <si>
     <t xml:space="preserve">take plet 1 ;
-狼患=9 ;
+wolf=9 ;
 gold+80</t>
   </si>
   <si>
@@ -457,7 +457,7 @@
     <t>see</t>
   </si>
   <si>
-    <t>狼患==9 &amp;&amp; !_grudge</t>
+    <t>wolf==9 &amp;&amp; !_grudge</t>
   </si>
   <si>
     <t>喂！你給我過來！</t>
@@ -472,30 +472,30 @@
     <t>最近黑森林的狼變多了，肉舖都要沒貨了……能幫我獵些狼皮回來嗎？</t>
   </si>
   <si>
-    <t xml:space="preserve">狼患=1 ;
-count 狼患.殺狼 kill:wolf</t>
+    <t xml:space="preserve">wolf=1 ;
+count wolf.kills kill:wolf</t>
   </si>
   <si>
     <t>n_wolf_report</t>
   </si>
   <si>
-    <t xml:space="preserve">狼患&lt;4 : 狼皮收集得如何了? ;
-狼患==4 : 都準備好了嗎？太好了! ;
-狼患==10 : 謝謝你，這是你的獎勵</t>
-  </si>
-  <si>
-    <t>狼患&lt;4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">狼患=10 ;
+    <t xml:space="preserve">wolf&lt;4 : 狼皮收集得如何了? ;
+wolf==4 : 都準備好了嗎？太好了! ;
+wolf==10 : 謝謝你，這是你的獎勵</t>
+  </si>
+  <si>
+    <t>wolf&lt;4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wolf=10 ;
 gold+120 ;
 give axe_01 1</t>
   </si>
   <si>
-    <t>狼患==4</t>
-  </si>
-  <si>
-    <t>狼患==10</t>
+    <t>wolf==4</t>
+  </si>
+  <si>
+    <t>wolf==10</t>
   </si>
   <si>
     <t>n_wolf_karen</t>
@@ -508,7 +508,7 @@
   </si>
   <si>
     <t xml:space="preserve">take plet 1 ;
-狼患=4</t>
+wolf=4</t>
   </si>
   <si>
     <t>n_wolf_grudge</t>
@@ -521,20 +521,20 @@
   </si>
   <si>
     <t xml:space="preserve">_grudge=1 ;
-好感-5</t>
+favor-5</t>
   </si>
   <si>
     <t>我想賣給誰就賣給誰</t>
   </si>
   <si>
     <t xml:space="preserve">_grudge=1 ;
-好感-15</t>
-  </si>
-  <si>
-    <t>狼群</t>
-  </si>
-  <si>
-    <t>狼患 &amp;&amp; 狼患&lt;9</t>
+favor-15</t>
+  </si>
+  <si>
+    <t>wolves</t>
+  </si>
+  <si>
+    <t>wolf &amp;&amp; wolf&lt;9</t>
   </si>
   <si>
     <t>狼患進行中，m_03x05 出現 3 隻狼</t>
@@ -552,7 +552,7 @@
     <t>trade_ask</t>
   </si>
   <si>
-    <t>狼患==10 &amp;&amp; 狼皮生意==0</t>
+    <t>wolf==10 &amp;&amp; pelt_trade==0</t>
   </si>
   <si>
     <t>@n_trade_ask</t>
@@ -561,7 +561,7 @@
     <t>trade_karen</t>
   </si>
   <si>
-    <t>狼皮生意==1</t>
+    <t>pelt_trade==1</t>
   </si>
   <si>
     <t>轉達 xi 的提案</t>
@@ -573,7 +573,7 @@
     <t>trade_report</t>
   </si>
   <si>
-    <t>狼皮生意&gt;=1 &amp;&amp; 狼皮生意&lt;10</t>
+    <t>pelt_trade&gt;=1 &amp;&amp; pelt_trade&lt;10</t>
   </si>
   <si>
     <t>@n_trade_report</t>
@@ -585,25 +585,25 @@
     <t>森林安靜多了，這下該跟 karen 把長期收購狼皮的事情談攏。你能不能幫我帶個提案去，跟她把價錢跟數量談好？</t>
   </si>
   <si>
-    <t>狼皮生意=1</t>
+    <t>pelt_trade=1</t>
   </si>
   <si>
     <t>n_trade_report</t>
   </si>
   <si>
-    <t xml:space="preserve">狼皮生意==1 : 跟 karen 談得怎麼樣了? ;
-狼皮生意==2 : 都談好了嗎？太好了! ;
-狼皮生意==10 : 這趟辛苦你了，這是謝禮</t>
-  </si>
-  <si>
-    <t xml:space="preserve">狼皮生意=10 ;
+    <t xml:space="preserve">pelt_trade==1 : 跟 karen 談得怎麼樣了? ;
+pelt_trade==2 : 都談好了嗎？太好了! ;
+pelt_trade==10 : 這趟辛苦你了，這是謝禮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pelt_trade=10 ;
 gold+100</t>
   </si>
   <si>
-    <t>狼皮生意==2</t>
-  </si>
-  <si>
-    <t>狼皮生意==10</t>
+    <t>pelt_trade==2</t>
+  </si>
+  <si>
+    <t>pelt_trade==10</t>
   </si>
   <si>
     <t>n_trade_karen</t>
@@ -612,7 +612,7 @@
     <t>長期收購？聽起來不錯，價錢我可以再加一點，你回去跟 xi 說一聲，這筆生意我接了。</t>
   </si>
   <si>
-    <t>狼皮生意=2</t>
+    <t>pelt_trade=2</t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1865,7 +1865,7 @@
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" ht="126" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" ht="126" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="7" t="s">
         <v>19</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1939,7 +1939,7 @@
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1954,7 +1954,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1969,7 +1969,7 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="7"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="J6" s="14"/>
     </row>
-    <row r="7" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="9"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -2003,8 +2003,7 @@
       </c>
       <c r="J7" s="10"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="9" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -2039,7 +2038,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>120</v>
       </c>
@@ -2061,7 +2060,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>123</v>
       </c>
@@ -2081,7 +2080,7 @@
       </c>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>126</v>
       </c>
@@ -2101,7 +2100,7 @@
       </c>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
         <v>129</v>
       </c>
@@ -2123,7 +2122,7 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
         <v>133</v>
       </c>
@@ -2145,7 +2144,7 @@
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" ht="47.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" ht="47.25" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
         <v>136</v>
       </c>
@@ -2173,7 +2172,7 @@
       </c>
       <c r="K15" s="14"/>
     </row>
-    <row r="16" ht="31.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" ht="31.5" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>142</v>
       </c>
@@ -2197,8 +2196,7 @@
       </c>
       <c r="K16" s="17"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="15.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -2230,7 +2228,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="s">
         <v>84</v>
       </c>
@@ -2249,7 +2247,7 @@
       <c r="I19" s="14"/>
       <c r="J19" s="14"/>
     </row>
-    <row r="20" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="s">
         <v>87</v>
       </c>
@@ -2268,7 +2266,7 @@
       <c r="I20" s="14"/>
       <c r="J20" s="14"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="s">
         <v>87</v>
       </c>
@@ -2285,7 +2283,7 @@
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
     </row>
-    <row r="22" ht="94.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" ht="94.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="13" t="s">
         <v>84</v>
       </c>
@@ -2304,7 +2302,7 @@
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="13" t="s">
         <v>87</v>
       </c>
@@ -2323,7 +2321,7 @@
       </c>
       <c r="J23" s="14"/>
     </row>
-    <row r="24" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
         <v>87</v>
       </c>
@@ -2344,7 +2342,7 @@
       </c>
       <c r="J24" s="14"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" ht="15.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="13" t="s">
         <v>87</v>
       </c>
@@ -2363,7 +2361,7 @@
       </c>
       <c r="J25" s="14"/>
     </row>
-    <row r="26" ht="47.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
         <v>84</v>
       </c>
@@ -2382,7 +2380,7 @@
       <c r="I26" s="14"/>
       <c r="J26" s="14"/>
     </row>
-    <row r="27" ht="47.25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" ht="47.25" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="13" t="s">
         <v>87</v>
       </c>
@@ -2401,7 +2399,7 @@
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
     </row>
-    <row r="28" ht="63" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" ht="63" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="13" t="s">
         <v>84</v>
       </c>
@@ -2420,7 +2418,7 @@
       <c r="I28" s="14"/>
       <c r="J28" s="14"/>
     </row>
-    <row r="29" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="13" t="s">
         <v>87</v>
       </c>
@@ -2439,7 +2437,7 @@
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
     </row>
-    <row r="30" ht="31.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" ht="31.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="s">
         <v>87</v>
       </c>
@@ -2458,8 +2456,7 @@
       <c r="I30" s="17"/>
       <c r="J30" s="17"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="15.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -2473,7 +2470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" ht="31.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" ht="31.5" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>166</v>
       </c>

--- a/xls/story.xlsx
+++ b/xls/story.xlsx
@@ -73,7 +73,7 @@
     <t>討伐令的殺盜賊計數器（count 開、stop 停）</t>
   </si>
   <si>
-    <t>wolf</t>
+    <t>wolf_hunt</t>
   </si>
   <si>
     <t>屠夫的生意經</t>
@@ -82,7 +82,7 @@
     <t>xi 的狼皮委託：1 殺 3 隻狼 / 2 剝狼皮 / 3 狼皮交給 karen / 4 回報 xi / 10 完成</t>
   </si>
   <si>
-    <t>wolf.kills</t>
+    <t>wolf_hunt.kills</t>
   </si>
   <si>
     <t>狼患的殺狼計數器（count 開、stop 停）</t>
@@ -361,7 +361,7 @@
     <t>黑森林的野狼氾濫，xi 的肉舖快沒貨了，想找人幫忙獵狼取皮，順便帶個口信給城裡的商人 karen。</t>
   </si>
   <si>
-    <t>前往黑森林狩獵，擊殺野狼 ({wolf.kills}/3)</t>
+    <t>前往黑森林狩獵，擊殺野狼 ({wolf_hunt.kills}/3)</t>
   </si>
   <si>
     <t>金幣 x120、斧頭 x1</t>
@@ -385,7 +385,7 @@
     <t>wolf_ask</t>
   </si>
   <si>
-    <t>wolf==0</t>
+    <t>wolf_hunt==0</t>
   </si>
   <si>
     <t>@n_wolf_ask</t>
@@ -394,26 +394,26 @@
     <t>wolf_kill</t>
   </si>
   <si>
-    <t>wolf==1 &amp;&amp; wolf.kills&gt;=3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wolf=2 ;
-stop wolf.kills</t>
+    <t>wolf_hunt==1 &amp;&amp; wolf_hunt.kills&gt;=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wolf_hunt=2 ;
+stop wolf_hunt.kills</t>
   </si>
   <si>
     <t>wolf_pelt</t>
   </si>
   <si>
-    <t>wolf==2 &amp;&amp; item:plet:1</t>
-  </si>
-  <si>
-    <t>wolf=3</t>
+    <t>wolf_hunt==2 &amp;&amp; item:plet:1</t>
+  </si>
+  <si>
+    <t>wolf_hunt=3</t>
   </si>
   <si>
     <t>wolf_karen</t>
   </si>
   <si>
-    <t>wolf==3 &amp;&amp; item:plet:1</t>
+    <t>wolf_hunt==3 &amp;&amp; item:plet:1</t>
   </si>
   <si>
     <t>關於黑森林的狼皮</t>
@@ -425,7 +425,7 @@
     <t>wolf_report</t>
   </si>
   <si>
-    <t>wolf&gt;=1 &amp;&amp; wolf&lt;9</t>
+    <t>wolf_hunt&gt;=1 &amp;&amp; wolf_hunt&lt;9</t>
   </si>
   <si>
     <t>@n_wolf_report</t>
@@ -434,7 +434,7 @@
     <t>wolf_sell</t>
   </si>
   <si>
-    <t>wolf==2</t>
+    <t>wolf_hunt==2</t>
   </si>
   <si>
     <t>把狼皮直接賣給你</t>
@@ -447,7 +447,7 @@
   </si>
   <si>
     <t xml:space="preserve">take plet 1 ;
-wolf=9 ;
+wolf_hunt=9 ;
 gold+80</t>
   </si>
   <si>
@@ -457,7 +457,7 @@
     <t>see</t>
   </si>
   <si>
-    <t>wolf==9 &amp;&amp; !_grudge</t>
+    <t>wolf_hunt==9 &amp;&amp; !_grudge</t>
   </si>
   <si>
     <t>喂！你給我過來！</t>
@@ -472,30 +472,30 @@
     <t>最近黑森林的狼變多了，肉舖都要沒貨了……能幫我獵些狼皮回來嗎？</t>
   </si>
   <si>
-    <t xml:space="preserve">wolf=1 ;
-count wolf.kills kill:wolf</t>
+    <t xml:space="preserve">wolf_hunt=1 ;
+count wolf_hunt.kills kill:wolf</t>
   </si>
   <si>
     <t>n_wolf_report</t>
   </si>
   <si>
-    <t xml:space="preserve">wolf&lt;4 : 狼皮收集得如何了? ;
-wolf==4 : 都準備好了嗎？太好了! ;
-wolf==10 : 謝謝你，這是你的獎勵</t>
-  </si>
-  <si>
-    <t>wolf&lt;4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wolf=10 ;
+    <t xml:space="preserve">wolf_hunt&lt;4 : 狼皮收集得如何了? ;
+wolf_hunt==4 : 都準備好了嗎？太好了! ;
+wolf_hunt==10 : 謝謝你，這是你的獎勵</t>
+  </si>
+  <si>
+    <t>wolf_hunt&lt;4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wolf_hunt=10 ;
 gold+120 ;
 give axe_01 1</t>
   </si>
   <si>
-    <t>wolf==4</t>
-  </si>
-  <si>
-    <t>wolf==10</t>
+    <t>wolf_hunt==4</t>
+  </si>
+  <si>
+    <t>wolf_hunt==10</t>
   </si>
   <si>
     <t>n_wolf_karen</t>
@@ -508,7 +508,7 @@
   </si>
   <si>
     <t xml:space="preserve">take plet 1 ;
-wolf=4</t>
+wolf_hunt=4</t>
   </si>
   <si>
     <t>n_wolf_grudge</t>
@@ -534,7 +534,7 @@
     <t>wolves</t>
   </si>
   <si>
-    <t>wolf &amp;&amp; wolf&lt;9</t>
+    <t>wolf_hunt &amp;&amp; wolf_hunt&lt;9</t>
   </si>
   <si>
     <t>狼患進行中，m_03x05 出現 3 隻狼</t>
@@ -552,7 +552,7 @@
     <t>trade_ask</t>
   </si>
   <si>
-    <t>wolf==10 &amp;&amp; pelt_trade==0</t>
+    <t>wolf_hunt==10 &amp;&amp; pelt_trade==0</t>
   </si>
   <si>
     <t>@n_trade_ask</t>
